--- a/playwright-test/test-data/input/test-cases.xlsx
+++ b/playwright-test/test-data/input/test-cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489A05FB-BC42-4615-B5F6-E38F2EADC729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E04A44C-5EB6-46FF-97A6-EEA4DA58A3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -294,13 +294,13 @@
     <t>[data-sonner-toast]</t>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
     <t>Tài khoản hoặc mật khẩu không chính xác</t>
   </si>
   <si>
     <t>Email cần ít nhất 3 kí tự</t>
+  </si>
+  <si>
+    <t>/home</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1136,7 @@
         <v>26</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>26</v>
@@ -1223,7 +1223,7 @@
         <v>26</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I9" s="7"/>
     </row>
@@ -1540,7 +1540,7 @@
         <v>26</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>26</v>
